--- a/財務管理表.xlsx
+++ b/財務管理表.xlsx
@@ -18,10 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -103,7 +102,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -165,11 +164,93 @@
         <color rgb="002E75B6"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="002E75B6"/>
+      </left>
+      <right style="thin">
+        <color rgb="002E75B6"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="medium">
+        <color rgb="002E75B6"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="002E75B6"/>
+      </right>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="002E75B6"/>
+      </right>
+      <top style="thin"/>
+      <bottom style="medium">
+        <color rgb="002E75B6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002E75B6"/>
+      </left>
+      <right style="thin">
+        <color rgb="002E75B6"/>
+      </right>
+      <top style="medium">
+        <color rgb="002E75B6"/>
+      </top>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002E75B6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="002E75B6"/>
+      </right>
+      <top style="medium">
+        <color rgb="002E75B6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="002E75B6"/>
+      </right>
+      <top style="medium">
+        <color rgb="002E75B6"/>
+      </top>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -177,7 +258,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -188,14 +269,14 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -210,7 +291,7 @@
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -239,7 +320,32 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -320,7 +426,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -490,7 +595,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -632,7 +736,6 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1048,7 +1151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1154,7 +1257,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="24" t="n">
         <v>46054</v>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1167,7 +1270,7 @@
         <f>B3-C3</f>
         <v/>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="25">
         <f>IF(B3=0,"",H3/B3)</f>
         <v/>
       </c>
@@ -1179,14 +1282,14 @@
         <f>H3-J3</f>
         <v/>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="25">
         <f>IF(B3=0,"",K3/B3)</f>
         <v/>
       </c>
       <c r="M3" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="26" t="n">
         <v>46055</v>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1199,7 +1302,7 @@
         <f>B4-C4</f>
         <v/>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="25">
         <f>IF(B4=0,"",H4/B4)</f>
         <v/>
       </c>
@@ -1211,14 +1314,14 @@
         <f>H4-J4</f>
         <v/>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="25">
         <f>IF(B4=0,"",K4/B4)</f>
         <v/>
       </c>
       <c r="M4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="24" t="n">
         <v>46056</v>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -1231,7 +1334,7 @@
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="25">
         <f>IF(B5=0,"",H5/B5)</f>
         <v/>
       </c>
@@ -1243,14 +1346,14 @@
         <f>H5-J5</f>
         <v/>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="25">
         <f>IF(B5=0,"",K5/B5)</f>
         <v/>
       </c>
       <c r="M5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="26" t="n">
         <v>46057</v>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -1263,7 +1366,7 @@
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="25">
         <f>IF(B6=0,"",H6/B6)</f>
         <v/>
       </c>
@@ -1275,14 +1378,14 @@
         <f>H6-J6</f>
         <v/>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="25">
         <f>IF(B6=0,"",K6/B6)</f>
         <v/>
       </c>
       <c r="M6" s="7" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="24" t="n">
         <v>46058</v>
       </c>
       <c r="B7" s="4" t="n"/>
@@ -1295,7 +1398,7 @@
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="25">
         <f>IF(B7=0,"",H7/B7)</f>
         <v/>
       </c>
@@ -1307,14 +1410,14 @@
         <f>H7-J7</f>
         <v/>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="25">
         <f>IF(B7=0,"",K7/B7)</f>
         <v/>
       </c>
       <c r="M7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="26" t="n">
         <v>46059</v>
       </c>
       <c r="B8" s="4" t="n"/>
@@ -1327,7 +1430,7 @@
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="25">
         <f>IF(B8=0,"",H8/B8)</f>
         <v/>
       </c>
@@ -1339,14 +1442,14 @@
         <f>H8-J8</f>
         <v/>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="25">
         <f>IF(B8=0,"",K8/B8)</f>
         <v/>
       </c>
       <c r="M8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="24" t="n">
         <v>46060</v>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -1359,7 +1462,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="25">
         <f>IF(B9=0,"",H9/B9)</f>
         <v/>
       </c>
@@ -1371,14 +1474,14 @@
         <f>H9-J9</f>
         <v/>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="25">
         <f>IF(B9=0,"",K9/B9)</f>
         <v/>
       </c>
       <c r="M9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="26" t="n">
         <v>46061</v>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -1391,7 +1494,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="25">
         <f>IF(B10=0,"",H10/B10)</f>
         <v/>
       </c>
@@ -1403,14 +1506,14 @@
         <f>H10-J10</f>
         <v/>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="25">
         <f>IF(B10=0,"",K10/B10)</f>
         <v/>
       </c>
       <c r="M10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="24" t="n">
         <v>46062</v>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -1423,7 +1526,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="25">
         <f>IF(B11=0,"",H11/B11)</f>
         <v/>
       </c>
@@ -1435,14 +1538,14 @@
         <f>H11-J11</f>
         <v/>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="25">
         <f>IF(B11=0,"",K11/B11)</f>
         <v/>
       </c>
       <c r="M11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="26" t="n">
         <v>46063</v>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -1455,7 +1558,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="25">
         <f>IF(B12=0,"",H12/B12)</f>
         <v/>
       </c>
@@ -1467,14 +1570,14 @@
         <f>H12-J12</f>
         <v/>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="25">
         <f>IF(B12=0,"",K12/B12)</f>
         <v/>
       </c>
       <c r="M12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="24" t="n">
         <v>46064</v>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -1487,7 +1590,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="25">
         <f>IF(B13=0,"",H13/B13)</f>
         <v/>
       </c>
@@ -1499,14 +1602,14 @@
         <f>H13-J13</f>
         <v/>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="25">
         <f>IF(B13=0,"",K13/B13)</f>
         <v/>
       </c>
       <c r="M13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="26" t="n">
         <v>46065</v>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -1519,7 +1622,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="25">
         <f>IF(B14=0,"",H14/B14)</f>
         <v/>
       </c>
@@ -1531,14 +1634,14 @@
         <f>H14-J14</f>
         <v/>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="25">
         <f>IF(B14=0,"",K14/B14)</f>
         <v/>
       </c>
       <c r="M14" s="7" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="24" t="n">
         <v>46066</v>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -1551,7 +1654,7 @@
         <f>B15-C15</f>
         <v/>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="25">
         <f>IF(B15=0,"",H15/B15)</f>
         <v/>
       </c>
@@ -1563,14 +1666,14 @@
         <f>H15-J15</f>
         <v/>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="25">
         <f>IF(B15=0,"",K15/B15)</f>
         <v/>
       </c>
       <c r="M15" s="7" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="26" t="n">
         <v>46067</v>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1583,7 +1686,7 @@
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="25">
         <f>IF(B16=0,"",H16/B16)</f>
         <v/>
       </c>
@@ -1595,14 +1698,14 @@
         <f>H16-J16</f>
         <v/>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="25">
         <f>IF(B16=0,"",K16/B16)</f>
         <v/>
       </c>
       <c r="M16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="24" t="n">
         <v>46068</v>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1615,7 +1718,7 @@
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="25">
         <f>IF(B17=0,"",H17/B17)</f>
         <v/>
       </c>
@@ -1627,14 +1730,14 @@
         <f>H17-J17</f>
         <v/>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="25">
         <f>IF(B17=0,"",K17/B17)</f>
         <v/>
       </c>
       <c r="M17" s="7" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="26" t="n">
         <v>46069</v>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1647,7 +1750,7 @@
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="25">
         <f>IF(B18=0,"",H18/B18)</f>
         <v/>
       </c>
@@ -1659,14 +1762,14 @@
         <f>H18-J18</f>
         <v/>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="25">
         <f>IF(B18=0,"",K18/B18)</f>
         <v/>
       </c>
       <c r="M18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="24" t="n">
         <v>46070</v>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1679,7 +1782,7 @@
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="25">
         <f>IF(B19=0,"",H19/B19)</f>
         <v/>
       </c>
@@ -1691,14 +1794,14 @@
         <f>H19-J19</f>
         <v/>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="25">
         <f>IF(B19=0,"",K19/B19)</f>
         <v/>
       </c>
       <c r="M19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="26" t="n">
         <v>46071</v>
       </c>
       <c r="B20" s="4" t="n"/>
@@ -1711,7 +1814,7 @@
         <f>B20-C20</f>
         <v/>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="25">
         <f>IF(B20=0,"",H20/B20)</f>
         <v/>
       </c>
@@ -1723,14 +1826,14 @@
         <f>H20-J20</f>
         <v/>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="25">
         <f>IF(B20=0,"",K20/B20)</f>
         <v/>
       </c>
       <c r="M20" s="7" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="24" t="n">
         <v>46072</v>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1743,7 +1846,7 @@
         <f>B21-C21</f>
         <v/>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="25">
         <f>IF(B21=0,"",H21/B21)</f>
         <v/>
       </c>
@@ -1755,14 +1858,14 @@
         <f>H21-J21</f>
         <v/>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="25">
         <f>IF(B21=0,"",K21/B21)</f>
         <v/>
       </c>
       <c r="M21" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="26" t="n">
         <v>46073</v>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1775,7 +1878,7 @@
         <f>B22-C22</f>
         <v/>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="25">
         <f>IF(B22=0,"",H22/B22)</f>
         <v/>
       </c>
@@ -1787,14 +1890,14 @@
         <f>H22-J22</f>
         <v/>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="25">
         <f>IF(B22=0,"",K22/B22)</f>
         <v/>
       </c>
       <c r="M22" s="7" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="24" t="n">
         <v>46074</v>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1807,7 +1910,7 @@
         <f>B23-C23</f>
         <v/>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="25">
         <f>IF(B23=0,"",H23/B23)</f>
         <v/>
       </c>
@@ -1819,14 +1922,14 @@
         <f>H23-J23</f>
         <v/>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="25">
         <f>IF(B23=0,"",K23/B23)</f>
         <v/>
       </c>
       <c r="M23" s="7" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="26" t="n">
         <v>46075</v>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1839,7 +1942,7 @@
         <f>B24-C24</f>
         <v/>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="25">
         <f>IF(B24=0,"",H24/B24)</f>
         <v/>
       </c>
@@ -1851,14 +1954,14 @@
         <f>H24-J24</f>
         <v/>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="25">
         <f>IF(B24=0,"",K24/B24)</f>
         <v/>
       </c>
       <c r="M24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="24" t="n">
         <v>46076</v>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1871,7 +1974,7 @@
         <f>B25-C25</f>
         <v/>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="25">
         <f>IF(B25=0,"",H25/B25)</f>
         <v/>
       </c>
@@ -1883,14 +1986,14 @@
         <f>H25-J25</f>
         <v/>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="25">
         <f>IF(B25=0,"",K25/B25)</f>
         <v/>
       </c>
       <c r="M25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="26" t="n">
         <v>46077</v>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1903,7 +2006,7 @@
         <f>B26-C26</f>
         <v/>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="25">
         <f>IF(B26=0,"",H26/B26)</f>
         <v/>
       </c>
@@ -1915,14 +2018,14 @@
         <f>H26-J26</f>
         <v/>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="25">
         <f>IF(B26=0,"",K26/B26)</f>
         <v/>
       </c>
       <c r="M26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="24" t="n">
         <v>46078</v>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1935,7 +2038,7 @@
         <f>B27-C27</f>
         <v/>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="25">
         <f>IF(B27=0,"",H27/B27)</f>
         <v/>
       </c>
@@ -1947,14 +2050,14 @@
         <f>H27-J27</f>
         <v/>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="25">
         <f>IF(B27=0,"",K27/B27)</f>
         <v/>
       </c>
       <c r="M27" s="7" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="26" t="n">
         <v>46079</v>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1967,7 +2070,7 @@
         <f>B28-C28</f>
         <v/>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="25">
         <f>IF(B28=0,"",H28/B28)</f>
         <v/>
       </c>
@@ -1979,14 +2082,14 @@
         <f>H28-J28</f>
         <v/>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="25">
         <f>IF(B28=0,"",K28/B28)</f>
         <v/>
       </c>
       <c r="M28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="24" t="n">
         <v>46080</v>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1999,7 +2102,7 @@
         <f>B29-C29</f>
         <v/>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="25">
         <f>IF(B29=0,"",H29/B29)</f>
         <v/>
       </c>
@@ -2011,14 +2114,14 @@
         <f>H29-J29</f>
         <v/>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="25">
         <f>IF(B29=0,"",K29/B29)</f>
         <v/>
       </c>
       <c r="M29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="26" t="n">
         <v>46081</v>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -2031,7 +2134,7 @@
         <f>B30-C30</f>
         <v/>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="25">
         <f>IF(B30=0,"",H30/B30)</f>
         <v/>
       </c>
@@ -2043,127 +2146,63 @@
         <f>H30-J30</f>
         <v/>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="25">
         <f>IF(B30=0,"",K30/B30)</f>
         <v/>
       </c>
       <c r="M30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>46082</v>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="5">
-        <f>B31-C31</f>
-        <v/>
-      </c>
-      <c r="I31" s="6">
-        <f>IF(B31=0,"",H31/B31)</f>
-        <v/>
-      </c>
-      <c r="J31" s="5">
-        <f>D31+E31+F31+G31</f>
-        <v/>
-      </c>
-      <c r="K31" s="5">
-        <f>H31-J31</f>
-        <v/>
-      </c>
-      <c r="L31" s="6">
-        <f>IF(B31=0,"",K31/B31)</f>
-        <v/>
-      </c>
-      <c r="M31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="n">
-        <v>46083</v>
-      </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="5">
-        <f>B32-C32</f>
-        <v/>
-      </c>
-      <c r="I32" s="6">
-        <f>IF(B32=0,"",H32/B32)</f>
-        <v/>
-      </c>
-      <c r="J32" s="5">
-        <f>D32+E32+F32+G32</f>
-        <v/>
-      </c>
-      <c r="K32" s="5">
-        <f>H32-J32</f>
-        <v/>
-      </c>
-      <c r="L32" s="6">
-        <f>IF(B32=0,"",K32/B32)</f>
-        <v/>
-      </c>
-      <c r="M32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>合計 Total</t>
         </is>
       </c>
-      <c r="B33" s="10">
+      <c r="B31" s="10">
         <f>SUM(B3:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="10">
+      <c r="C31" s="10">
         <f>SUM(C3:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="10">
+      <c r="D31" s="10">
         <f>SUM(D3:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="10">
+      <c r="E31" s="10">
         <f>SUM(E3:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="10">
+      <c r="F31" s="10">
         <f>SUM(F3:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="10">
+      <c r="G31" s="10">
         <f>SUM(G3:G32)</f>
         <v/>
       </c>
-      <c r="H33" s="11">
+      <c r="H31" s="11">
         <f>SUM(H3:H32)</f>
         <v/>
       </c>
-      <c r="I33" s="12">
+      <c r="I31" s="27">
         <f>IF(B33=0,"",H33/B33)</f>
         <v/>
       </c>
-      <c r="J33" s="11">
+      <c r="J31" s="11">
         <f>SUM(J3:J32)</f>
         <v/>
       </c>
-      <c r="K33" s="11">
+      <c r="K31" s="11">
         <f>SUM(K3:K32)</f>
         <v/>
       </c>
-      <c r="L33" s="12">
+      <c r="L31" s="27">
         <f>IF(B33=0,"",K33/B33)</f>
         <v/>
       </c>
-      <c r="M33" s="13" t="n"/>
+      <c r="M31" s="13" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="0" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
@@ -2273,7 +2312,7 @@
         <f>B3-C3</f>
         <v/>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="25">
         <f>IF(B3=0,"",D3/B3)</f>
         <v/>
       </c>
@@ -2285,7 +2324,7 @@
         <f>D3-F3</f>
         <v/>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="25">
         <f>IF(B3=0,"",G3/B3)</f>
         <v/>
       </c>
@@ -2308,7 +2347,7 @@
         <f>B4-C4</f>
         <v/>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="25">
         <f>IF(B4=0,"",D4/B4)</f>
         <v/>
       </c>
@@ -2320,7 +2359,7 @@
         <f>D4-F4</f>
         <v/>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="25">
         <f>IF(B4=0,"",G4/B4)</f>
         <v/>
       </c>
@@ -2343,7 +2382,7 @@
         <f>B5-C5</f>
         <v/>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="25">
         <f>IF(B5=0,"",D5/B5)</f>
         <v/>
       </c>
@@ -2355,7 +2394,7 @@
         <f>D5-F5</f>
         <v/>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="25">
         <f>IF(B5=0,"",G5/B5)</f>
         <v/>
       </c>
@@ -2378,7 +2417,7 @@
         <f>B6-C6</f>
         <v/>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="25">
         <f>IF(B6=0,"",D6/B6)</f>
         <v/>
       </c>
@@ -2390,7 +2429,7 @@
         <f>D6-F6</f>
         <v/>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="25">
         <f>IF(B6=0,"",G6/B6)</f>
         <v/>
       </c>
@@ -2413,7 +2452,7 @@
         <f>B7-C7</f>
         <v/>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="25">
         <f>IF(B7=0,"",D7/B7)</f>
         <v/>
       </c>
@@ -2425,7 +2464,7 @@
         <f>D7-F7</f>
         <v/>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="25">
         <f>IF(B7=0,"",G7/B7)</f>
         <v/>
       </c>
@@ -2448,7 +2487,7 @@
         <f>B8-C8</f>
         <v/>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="25">
         <f>IF(B8=0,"",D8/B8)</f>
         <v/>
       </c>
@@ -2460,7 +2499,7 @@
         <f>D8-F8</f>
         <v/>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="25">
         <f>IF(B8=0,"",G8/B8)</f>
         <v/>
       </c>
@@ -2483,7 +2522,7 @@
         <f>B9-C9</f>
         <v/>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="25">
         <f>IF(B9=0,"",D9/B9)</f>
         <v/>
       </c>
@@ -2495,7 +2534,7 @@
         <f>D9-F9</f>
         <v/>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="25">
         <f>IF(B9=0,"",G9/B9)</f>
         <v/>
       </c>
@@ -2518,7 +2557,7 @@
         <f>B10-C10</f>
         <v/>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="25">
         <f>IF(B10=0,"",D10/B10)</f>
         <v/>
       </c>
@@ -2530,7 +2569,7 @@
         <f>D10-F10</f>
         <v/>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="25">
         <f>IF(B10=0,"",G10/B10)</f>
         <v/>
       </c>
@@ -2553,7 +2592,7 @@
         <f>B11-C11</f>
         <v/>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="25">
         <f>IF(B11=0,"",D11/B11)</f>
         <v/>
       </c>
@@ -2565,7 +2604,7 @@
         <f>D11-F11</f>
         <v/>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="25">
         <f>IF(B11=0,"",G11/B11)</f>
         <v/>
       </c>
@@ -2588,7 +2627,7 @@
         <f>B12-C12</f>
         <v/>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="25">
         <f>IF(B12=0,"",D12/B12)</f>
         <v/>
       </c>
@@ -2600,7 +2639,7 @@
         <f>D12-F12</f>
         <v/>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="25">
         <f>IF(B12=0,"",G12/B12)</f>
         <v/>
       </c>
@@ -2623,7 +2662,7 @@
         <f>B13-C13</f>
         <v/>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="25">
         <f>IF(B13=0,"",D13/B13)</f>
         <v/>
       </c>
@@ -2635,7 +2674,7 @@
         <f>D13-F13</f>
         <v/>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="25">
         <f>IF(B13=0,"",G13/B13)</f>
         <v/>
       </c>
@@ -2658,7 +2697,7 @@
         <f>B14-C14</f>
         <v/>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="25">
         <f>IF(B14=0,"",D14/B14)</f>
         <v/>
       </c>
@@ -2670,7 +2709,7 @@
         <f>D14-F14</f>
         <v/>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="25">
         <f>IF(B14=0,"",G14/B14)</f>
         <v/>
       </c>
@@ -2694,7 +2733,7 @@
         <f>SUM(D3:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="27">
         <f>IF(B15=0,"",D15/B15)</f>
         <v/>
       </c>
@@ -2706,7 +2745,7 @@
         <f>SUM(G3:G14)</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="27">
         <f>IF(B15=0,"",G15/B15)</f>
         <v/>
       </c>
@@ -2749,44 +2788,44 @@
       </c>
     </row>
     <row r="3" ht="35" customHeight="1">
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>本月營收
 Revenue</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n"/>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="C3" s="29" t="n"/>
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>毛利率
 Gross Margin</t>
         </is>
       </c>
-      <c r="F3" s="20" t="n"/>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="F3" s="29" t="n"/>
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>營業利益
 Op. Income</t>
         </is>
       </c>
-      <c r="I3" s="20" t="n"/>
+      <c r="I3" s="29" t="n"/>
     </row>
     <row r="4" ht="50" customHeight="1">
-      <c r="B4" s="21">
+      <c r="B4" s="30">
         <f>'月報表 Monthly Summary'!B4</f>
         <v/>
       </c>
-      <c r="C4" s="22" t="n"/>
-      <c r="E4" s="23">
+      <c r="C4" s="31" t="n"/>
+      <c r="E4" s="32">
         <f>'月報表 Monthly Summary'!E4</f>
         <v/>
       </c>
-      <c r="F4" s="22" t="n"/>
-      <c r="H4" s="21">
+      <c r="F4" s="31" t="n"/>
+      <c r="H4" s="30">
         <f>'月報表 Monthly Summary'!G4</f>
         <v/>
       </c>
-      <c r="I4" s="22" t="n"/>
+      <c r="I4" s="31" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
